--- a/pre-processing/data_cleaned/phone.xlsx
+++ b/pre-processing/data_cleaned/phone.xlsx
@@ -22,10 +22,10 @@
     <t>title</t>
   </si>
   <si>
-    <t>image_path</t>
-  </si>
-  <si>
-    <t>thumbnail_url</t>
+    <t>image</t>
+  </si>
+  <si>
+    <t>url</t>
   </si>
   <si>
     <t>category</t>

--- a/pre-processing/data_cleaned/phone.xlsx
+++ b/pre-processing/data_cleaned/phone.xlsx
@@ -55,7 +55,7 @@
     <t>Củ Sạc Samsung Không Kèm Cáp 25W - Hàng Chính Hãng</t>
   </si>
   <si>
-    <t>Điện Thoại Samsung Galaxy A56 5G - Hàng Chính Hãng</t>
+    <t>Điện Thoại Samsung Galaxy A36 5G - Hàng Chính Hãng</t>
   </si>
   <si>
     <t>Điện Thoại Xiaomi Redmi 13 8GB/128GB - Hàng Chính Hãng</t>
@@ -67,10 +67,7 @@
     <t>Ốp Lưng Samsung Galaxy S25 Trong Suốt - Hàng chính hãng</t>
   </si>
   <si>
-    <t>Điện thoại Samsung Galaxy S25, Điện thoại AI, Tìm kiếm thông minh, Video camera đêm Nightography, Chip Snapdragon - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Điện thoại Xiaomi Redmi Note 14 6GB/128GB - Hàng Chính Hãng</t>
+    <t>Điện thoại Samsung Galaxy S25, Điện thoại AI, Tìm kiếm thông minh, Video camera đêm Nightography, Chip Snapdragon - Đã kích hoạt bảo hành điện tử - Hàng Chính Hãng</t>
   </si>
   <si>
     <t>Điện Thoại Samsung Galaxy A06 4GB/64GB - Hàng Chính Hãng</t>
@@ -85,10 +82,13 @@
     <t>Điện thoại POCO C75 (6GB/128GB) - Hàng Chính Hãng</t>
   </si>
   <si>
+    <t>Điện thoại Masstel izi 16 4G - Hàng chính hãng</t>
+  </si>
+  <si>
     <t>Điện Thoại Samsung Galaxy A06 4GB/128GB - Hàng Chính Hãng</t>
   </si>
   <si>
-    <t>Apple iPhone 16</t>
+    <t>Điện Thoại Samsung Galaxy A06 (4GB/128GB) - Hàng Chính Hãng</t>
   </si>
   <si>
     <t>Apple iPhone 16 Pro</t>
@@ -112,7 +112,7 @@
     <t>Điện thoại ZTE Libero 5G IV - 4GB/128GB Dimensity 700 , Kháng nước IP67 , Sạc nhanh 22,5W - Mới nguyên seal - Hàng nhập khẩu</t>
   </si>
   <si>
-    <t>iPhone 15 Plus</t>
+    <t>Máy Tính Bảng Samsung Galaxy Tab A9 Wifi 4GB/64GB - Hàng Chính Hãng</t>
   </si>
   <si>
     <t>iPhone 15</t>
@@ -178,9 +178,6 @@
     <t>Điện Thoại Samsung Galaxy A56 5G 8GB/128GB - Hàng Chính Hãng</t>
   </si>
   <si>
-    <t>Apple iPhone 16e</t>
-  </si>
-  <si>
     <t>Điện Thoại Realme C65 6GB/128GB - Hàng Chính Hãng</t>
   </si>
   <si>
@@ -199,108 +196,117 @@
     <t>Điện Thoại Xiaomi 14T Pro 5G 12GB/512GB - Hàng Chính Hãng</t>
   </si>
   <si>
+    <t>Điện thoại ZTE Blade A34 (4GB/64GB) Màn hình 6.6", Pin 5000mAh - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Điện Thoại Samsung Galaxy A16 5G 8GB/128GB - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Điện thoại Samsung Galaxy S24 FE - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Combo Máy đọc sách Amazon Kindle Paperwhite 6 (Gen 12th) Kèm Bao Da, Mới nguyên Seal - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Máy đọc sách Amazon Kindle Paperwhite 6 (Gen 12th), Mới nguyên Seal - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Điện thoại Realme V60 (6GB/128GB) 5G , Chíp Dimensity 6300, Rom tiếng việt - Hàng nhập khẩu</t>
+  </si>
+  <si>
+    <t>Điện thoại Samsung Galaxy A06 - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Apple iPhone 16 Plus</t>
+  </si>
+  <si>
+    <t>Điện Thoại Nokia 220 4G - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Điện Thoại Xiaomi Redmi Note 13 Pro 5G 8GB/128GB Snapdragon 7s Gen 2 , Màn OLED 120Hz, Rom Tiếng việt - Hàng nhập khẩu</t>
+  </si>
+  <si>
+    <t>Điện thoại Redmi Note 12R 5G 6/128GB Snapdragon 4 Gen 2, Rom Quốc tế có sẳn Tiếng việt - Hàng nhập khẩu</t>
+  </si>
+  <si>
+    <t>Điện thoại Masstel izi 16 4G(LTE) , Bàn phím nổi, FM không dây - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Điện Thoại Samsung Galaxy A05 4GB/64GB - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Điện Thoại Xiaomi Redmi Note 13 6GB/128GB - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Combo Máy đọc sách Kindle Scribe kèm bút – thế hệ đầu tiên có thể đọc và viết, màn hình 10,2” 300PPI, đèn vàng warmlight, bộ nhớ 16-64GB, đồng bộ dữ liệu qua Microsoft Word - hàng nhập khẩu</t>
+  </si>
+  <si>
+    <t>Máy đọc sách Boox Palma - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Điện thoại OPPO A58 6GB/128GB , Sạc nhanh 33W - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Điện thoại Xiaomi Redmi Note 10 JE 5G 4GB/64GB - Màn 90HZ - Chống Nước IP68 - Hàng Nhập Khẩu - Bản quốc tế</t>
+  </si>
+  <si>
+    <t>Combo Máy đọc sách All New Kindle Paperwhite 5 (11th Gen) và Bao da - Hàng nhập khẩu</t>
+  </si>
+  <si>
+    <t>Điện Thoại Bàn Panasonic KX-TSC11 - Hàng Chính Hãng - Trắng</t>
+  </si>
+  <si>
+    <t>Combo máy đọc sách Kindle Paperwhite 5 (11th gen) tặng kèm bao da ( Cover ) - Hàng nhập khẩu</t>
+  </si>
+  <si>
+    <t>Điện thoại bàn Panasonic KX-TGB110 hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Điện thoại bàn không dây Panasonic KX-TGC313 - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Điện thoại bàn không dây Panasonic KX-TGD310 - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Điện Thoại Samsung Galaxy A06 5G 4GB/64GB - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Điện Thoại Oppo A58 8GB/128GB - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Điện thoại Samsung Galaxy A26 5G (8GB/128GB) - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Điện Thoại Samsung Galaxy A26 5G 8GB/128GB - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Điện thoại Samsung Galaxy A06 5G (4GB/128GB) - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Điện thoại Smartphone Vivo Y19s siêu bền - RAM 4GB ROM 128GB - Màu đen và xanh - 5500mAh - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Điện thoại Samsung Galaxy A36 5G (8GB/128GB) - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Điện thoại Samsung Galaxy S25 Ultra (12GB/256GB) - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Điện Thoại Samsung Galaxy M15 5G 4GB/128GB - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Điện thoại Xiaomi Redmi Note 14 Pro+ 5G (8GB/256GB) - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Điện thoại Xiaomi Redmi A3 - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Điện Thoại Xiaomi Redmi A3 3GB/64GB - Hàng Chính Hãng</t>
+  </si>
+  <si>
     <t>Điện Thoại Samsung Galaxy A55 5G - Hàng Chính Hãng</t>
   </si>
   <si>
-    <t>Điện thoại ZTE Blade A34 (4GB/64GB) Màn hình 6.6", Pin 5000mAh - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Điện Thoại Samsung Galaxy A16 5G 8GB/128GB - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Máy đọc sách Amazon Kindle Paperwhite 6 (Gen 12th), Mới nguyên Seal - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Điện thoại Realme V60 (6GB/128GB) 5G , Chíp Dimensity 6300, Rom tiếng việt - Hàng nhập khẩu</t>
-  </si>
-  <si>
-    <t>Điện thoại Masstel izi 16 4G - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>[MỚI] Điện thoại vivo Y100 (8GB+256GB) - Hàng chính hãng - 1 Đổi 1 trong tháng đầu tiên - Bảo hành 12 tháng</t>
-  </si>
-  <si>
-    <t>Điện thoại Samsung Galaxy A06 - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Apple iPhone 16 Plus</t>
-  </si>
-  <si>
-    <t>Máy tính bảng Samsung Galaxy Tab A9+ 5G - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Điện thoại Redmi Note 12R 5G 6/128GB Snapdragon 4 Gen 2, Rom Quốc tế có sẳn Tiếng việt - Hàng nhập khẩu</t>
-  </si>
-  <si>
-    <t>Điện thoại Masstel izi 16 4G(LTE) , Bàn phím nổi, FM không dây - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Điện Thoại Samsung Galaxy A05 4GB/64GB - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Điện Thoại Xiaomi Redmi Note 13 6GB/128GB - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Máy đọc sách Boox Palma - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Điện thoại OPPO A58 6GB/128GB , Sạc nhanh 33W - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Điện thoại Xiaomi Redmi Note 10 JE 5G 4GB/64GB - Màn 90HZ - Chống Nước IP68 - Hàng Nhập Khẩu - Bản quốc tế</t>
-  </si>
-  <si>
-    <t>Combo Máy đọc sách All New Kindle Paperwhite 5 (11th Gen) và Bao da - Hàng nhập khẩu</t>
-  </si>
-  <si>
-    <t>Điện Thoại Bàn Panasonic KX-TSC11 - Hàng Chính Hãng - Trắng</t>
-  </si>
-  <si>
-    <t>Combo máy đọc sách Kindle Paperwhite 5 (11th gen) tặng kèm bao da ( Cover ) - Hàng nhập khẩu</t>
-  </si>
-  <si>
-    <t>Điện thoại bàn Panasonic KX-TGB110 hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Điện thoại bàn không dây Panasonic KX-TGC313 - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Điện thoại bàn không dây Panasonic KX-TGD310 - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Điện Thoại Samsung Galaxy A06 5G 4GB/64GB - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Điện Thoại Oppo A58 8GB/128GB - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Điện thoại Samsung Galaxy A26 5G (8GB/128GB) - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Điện Thoại Samsung Galaxy A26 5G 8GB/128GB - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Điện thoại Samsung Galaxy A06 5G (4GB/128GB) - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Điện thoại Smartphone Vivo Y19s siêu bền - RAM 4GB ROM 128GB - Màu đen và xanh - 5500mAh - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Điện thoại Samsung Galaxy A36 5G (8GB/128GB) - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Điện Thoại Samsung Galaxy M15 5G 4GB/128GB - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Điện thoại Xiaomi Redmi Note 14 Pro+ 5G (8GB/256GB) - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Điện thoại Xiaomi Redmi A3 - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Điện Thoại Xiaomi Redmi A3 3GB/64GB - Hàng Chính Hãng</t>
-  </si>
-  <si>
     <t>Điện thoại Realme Note 50 , Màn 90HZ (3GB/64GB) Rom quốc tế - Hàng chính hãng</t>
   </si>
   <si>
@@ -316,322 +322,316 @@
     <t>Máy đọc sách Kindle Colorsoft Signature Edition 32Gb, Màn hình màu 7 inch - Hàng chính hãng</t>
   </si>
   <si>
-    <t>Điện thoại Samsung Galaxy S24 FE - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Combo Máy đọc sách Amazon Kindle Paperwhite 6 (Gen 12th) Kèm Bao Da, Mới nguyên Seal - Hàng chính hãng</t>
-  </si>
-  <si>
     <t>Xiaomi Redmi Note 12 5G 8GB/128GB ,Màn AMOLED 120Hz , Snapdragon 4 Gen 1 ,Sạc 33W ,Rom tiếng việt - Hàng nhập khẩu</t>
   </si>
   <si>
     <t>Điện Thoại Xiaomi Redmi 14C 4GB/128GB - Hàng Chính Hãng</t>
   </si>
   <si>
-    <t>images/phone/product_278237932.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_278098703.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_278000720.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277930407.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277777809.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277619147.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277614251.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277574339.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277465334.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277360579.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277175913.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277164932.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277063012.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277007015.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_276944892.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_276614493.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_276539826.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_276515327.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_276274790.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_276110349.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_276110023.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_276109904.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_276046675.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_275913708.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_275716541.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_275510578.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_274191773.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_271967379.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_271966786.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_270975124.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_252586291.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_203661802.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_197214029.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_184059211.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_181927774.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_181452535.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_170165701.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_164318603.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_163914808.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_125182567.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_278219968.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_278219887.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277812880.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277811118.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277737629.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277737595.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277646748.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277512620.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277512611.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277409699.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277311651.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277311630.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277164948.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277068413.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277065642.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277041250.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277039291.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277014407.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_276639232.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_276448920.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_276410628.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_276314708.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_276305472.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_276281988.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_276110276.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_275338696.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_274544634.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_274516951.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_274405521.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_273990229.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_272222033.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_271954384.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_271128271.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_230155305.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_217706932.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_204237269.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_201067649.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_164213695.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_23142193.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_11251770.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277944334.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277738691.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277707642.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277704510.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277651890.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277607297.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277490201.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277437876.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277356193.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277356031.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277175955.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_277030799.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_276944868.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_276925932.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_276802409.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_276500230.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_276489194.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_276465090.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_276099688.jpg</t>
-  </si>
-  <si>
-    <t>images/phone/product_276062770.jpg</t>
+    <t>images/phone/278237932.png</t>
+  </si>
+  <si>
+    <t>images/phone/278098703.png</t>
+  </si>
+  <si>
+    <t>images/phone/278000720.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277930407.png</t>
+  </si>
+  <si>
+    <t>images/phone/277777809.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277619147.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277614251.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277574339.png</t>
+  </si>
+  <si>
+    <t>images/phone/277466537.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277360579.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277175913.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277164932.jpeg</t>
+  </si>
+  <si>
+    <t>images/phone/277063012.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/276944892.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/276614493.png</t>
+  </si>
+  <si>
+    <t>images/phone/276539826.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/276515327.png</t>
+  </si>
+  <si>
+    <t>images/phone/276314708.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/276274790.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/276250848.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/276110023.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/276109904.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/276046675.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/275913708.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/275716541.png</t>
+  </si>
+  <si>
+    <t>images/phone/275510578.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/274191773.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/273872197.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/271966786.png</t>
+  </si>
+  <si>
+    <t>images/phone/270975124.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/252586291.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/203661802.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/197214029.png</t>
+  </si>
+  <si>
+    <t>images/phone/184059211.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/181927774.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/181452535.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/170165701.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/164318603.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/163914808.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/125182567.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/278219968.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/278219887.png</t>
+  </si>
+  <si>
+    <t>images/phone/277812880.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277811118.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277737629.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277737595.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277646748.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277512620.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277512611.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277311651.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277311630.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277164948.jpeg</t>
+  </si>
+  <si>
+    <t>images/phone/277068413.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277065642.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277041250.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277014407.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/276639232.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/276489194.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/276465090.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/276448920.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/276410628.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/276281988.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/276110276.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/275386982.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/274638659.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/274544634.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/274516951.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/274405521.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/273990229.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/273227290.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/272222033.png</t>
+  </si>
+  <si>
+    <t>images/phone/271954384.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/271128271.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/230155305.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/217706932.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/204237269.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/201067649.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/164213695.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/23142193.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/11251770.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277944334.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277738691.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277707642.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277704510.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277651890.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277607297.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277490201.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277484785.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277437876.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277356193.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277356031.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277175955.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277039291.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/277030799.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/276944868.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/276925932.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/276802409.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/276500230.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/276099688.jpg</t>
+  </si>
+  <si>
+    <t>images/phone/276062770.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/c1/e9/8d/e2b2df05d04c50049f05af881d87d542.png</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ae/60/79/ba4891af421749cbac2fb155b6eb775f.png</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/32/bb/19/92488d2e751c6a1c5cc83cdaebfbb047.png</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/a4/06/5a/d2b6b8308c9c3969477a3b1166b94189.jpg</t>
@@ -640,10 +640,10 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/3e/c0/33/8b84b5235168b3659a9220325840d2b8.png</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e3/9d/b3/7a965246188ce9d42ea6041b66f707da.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/b7/2a/79/5a477585d8b95154800b3d577aac42f2.jpg</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/11/c0/90/7ed78d65848ac95cac6cf6c03b6edcd0.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/c3/3f/2b/0a42ce3a97fc8567a567dda4a39aed6b.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/12/7e/f3/3c3ec08f1ed95467925267f4d0ca9c45.jpg</t>
@@ -652,7 +652,7 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/28/e4/7f/d1f6c5467529914727d0d213b507a0c6.png</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/87/75/32/87ff301dd7ffd7517e0f5f254ee7fa2c.jpg</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/d3/8e/4b/45b8f590abab4a7178d43c281de95e2d.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/24/4a/2f/11d371022ec1e410bfbf7d8f95af10e7.jpg</t>
@@ -661,16 +661,13 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/e1/c1/5e/1bf4cc1277814ce3e40bf21423347578.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/bd/df/bf/e2f54e2a64684557e20728cc54c7b2c7.png</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/51/51/ff/cb9783a732f9a02e7fb3dbc56efde135.jpeg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/f9/e3/62/bba8a70cb872d2f5a135d96f362db6dd.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/0b/fb/e0/8b6b96db507c4d58a84c021a2f10bd34.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e6/77/8d/695ccf826070451961cb58f5afa5da57.jpg</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/5d/16/de/a736634e1ce4732ab4b84ecfeec34ebc.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/02/59/95/3897103ae79ab6e504d5178dbe2452b4.png</t>
@@ -682,13 +679,16 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/43/86/e1/1afc6036aa30fd8d02a7e9d67714913b.png</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/09/0e/5b/58aaf66e130a4127e9ebac714fff04fd.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/b2/03/08/b2d825989b029533bd116447827bdd5e.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/30/f1/ec/bbde43f59e7724c4c474bb81f388f98e.jpg</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/20/10/20/0590c71068184207b66d1a0e6cd6e0af.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/0d/64/88/995ebf4252e69abc844a03650cbab4f0.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/71/d2/62/7b211c60c0e8717b20208a8a134d473c.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ba/09/35/200c7cc330da71f253391bc35e5ddbd0.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/5b/b5/d0/3b6f81dedb9cae1b9b040fff9943fa26.jpg</t>
@@ -703,16 +703,16 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/8a/24/b2/d6e6dc51c2c1b900768cb8a4ad4417e3.png</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/7d/31/b4/78b2a94b4eb466c0079d9061b5273b2c.jpg</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/39/35/a2/7f6aa04c1e1e9d7899dda7ef1a292bb1.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/81/00/e6/90ead980cb6221148ca246fc9c14e623.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/6c/6c/9e/a45bc5d76cec3c11c5f8cbcdf9e27929.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/eb/49/51/51c9ad1675f2b88999ca0689cdf207d7.png</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/be/f3/9b/89d7c9ad2a89a7c6642afe2f63a77e4b.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/6c/6c/9e/f3464d16a782e0d9ed5f74d98f155642.png</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/91/e7/7e/24461c4d1f848b11eaa4ff444f1ec5f9.jpg</t>
@@ -724,7 +724,7 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/ee/5e/ee/4ca7e4185f6f62d15437bef4b7dd552e.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/3b/95/ec/5b2c7ec0e09565f399a0a184bd71696b.png</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e9/81/46/e1287b85a10f7251c3dd02212a0784e3.png</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/b7/ba/88/66059a54a3a139d45841d412379b1fe4.jpg</t>
@@ -736,7 +736,7 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/31/4c/bf/255a33910828eebe5ddbb8cd86898409.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ee/92/92/def752a331e3d6c937308018f66aef33.jpg</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/47/17/1e/17c74931d1cc7232c3b55e7cc76ab1d2.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/dc/72/f9/bbe51405ebc1681123970efd01f32163.jpg</t>
@@ -748,13 +748,13 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/14/2f/c6/a161edd03cf817a13d4c3255d1467f0a.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/28/50/02/5fb991d06aa5c4ec4dbb735e224a868f.png</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/06/86/b4/83714e05899252ed2497c12553219ae0.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/02/4f/a6/5f33c000cfa27c67cd9204cbd32b65b9.png</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/4d/0f/9c/f699564af6cf0e909e900e1af6a91396.jpg</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/09/88/48/1c5b290a01698a63a6ff403cccbbc2e7.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/e8/04/c7/1cb4903ad84f0219e59b3f91ac7c6849.jpg</t>
@@ -763,31 +763,28 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/67/24/2d/17d53a9ca3b08d40d39bff3b6fb979cb.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/f4/96/f1/ab24f9ef9a2fc5b61cb282e0564272e2.jpg</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/54/43/66/455eeffaf69969ae183e6e8bf44649d9.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/0c/36/0b/88f7befba91e4d4ef67740f7b3661a67.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/1d/33/6b/a090d6f8da2d6a4b0e2fb94b37169ff4.jpg</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/a0/03/d8/548b454c8914aad6f4c0e05e5a50f5d9.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/5c/a1/f4/62101cca7d04b88a1d3ff68c4182451e.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/5e/7b/e4/a1b03a24fdf349a63fb539dd8953db20.jpg</t>
-  </si>
-  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/31/5f/bc/06e41b9dcc401fb97e5a66994e6d8aa9.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/d3/97/48/bf0115c0c1322c9ee0208930703db4da.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ff/dd/02/3a595bf99cc761d4c3805c9cc354a495.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/8f/ec/b9/18e68183cc93623f22250f21b76a2d61.jpg</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ae/8e/d5/3f2ff887140261456d472e6ab15c3d5a.jpeg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/8f/ec/b9/01d20b8675cedbe47fa69d1d18a32663.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/f9/e3/62/2f6952957b4b9f408cca4ea19ac429bf.jpg</t>
@@ -796,111 +793,120 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/04/b4/a7/056fe2c67be56d2f7a8d61016f86529d.jpg</t>
   </si>
   <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/8f/3d/d4/265222415e48466431578e5d50528ab8.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ba/fa/f2/518ce45e3aaccf3523b32321b7710d9a.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/6c/b1/87/9da32235b3a0d50ad5e2b3c5bb6a4a13.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/01/be/79/15314677596e5076541f60fc98999dbe.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/59/e7/74/68080c04130bb376a971ea54196b6f60.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/23/cc/4d/4e8dc54b550ca5438b8f3b4d5e786f7e.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/84/6c/56/782eb3f6491384553aaf71d0ac4f7661.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e8/84/2e/728d14c986750b780cc973f627161aa5.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/c2/86/5c/a027350956eb8d6ea6adc459ab55a6d8.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e2/46/d7/6c4179b0a95c74d323e44d2bb1c5bef5.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/43/b8/49/e2fc95922f52f6b546b3159e2e64454d.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/c0/be/c1/1856d5ff1185a7c14d038704c01a4269.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/fa/49/53/77a6b82103831b08839e78413b6a4046.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ea/6d/92/5917ee4c9a1124d82298b4695cd742b1.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/4d/40/63/8c5ddf03d01033f91bbc7cb5efd29c15.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/5c/39/8f/47a8209e6f2ec87da7a9d074610c834d.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/8c/80/88/c83c3f2fe6281a892666b5d3b3a0b963.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ce/82/d3/9bb25806d67aeb8ff3d583bcce9442e6.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/d4/e9/12/02af66cd50c05398bb27285f43905e85.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/7e/30/c9/e1b87f07a82762db5c122516dc5dd51c.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/84/dd/92/991b033392f01d334d1ce248d69e1daa.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/05/49/8f/e093321a9f3ed55fe77e8c83bfca8c55.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/77/b0/69/63bbae55fe5a5a096392c6d325e8fc95.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/d4/7e/c9/72e19580d556fa02d030cc6e77d1c6fd.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/c7/a1/73/79e54ec11e29656703784d7ad6eeae22.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/a5/a0/34/8d34647a6f97612e08a6869a6a7729ab.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/41/c4/04/18c6cf90e258545542577f9a2a9185c3.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/61/f7/fb/63445f959fb5036ba2504f7e1b91eecf.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/a7/fe/de/bc4d3269a46128e7c9c9ecb3f0e4c213.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/2c/63/b3/c84e4dd1cb2a41394e8086f52a26bd15.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/43/2c/ac/16c0f54cb6034936f9dcd799344bcb5a.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/02/52/15/e45e133fe9a563b67cb15e0c2c3e81dc.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/8e/8a/13/f3cf2027e7bdac3a34ca51e602191b5c.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/9b/82/57/da1f2bb909396656918a1ebcef4891b9.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/8e/29/10/17ea04e162b7f63bf7bc178b7597bb21.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/fd/51/c7/8782de5ed783270161ad63b17df30dc7.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/94/c2/a9/d47791500dc8a1c938439bcce17dbcc1.jpg</t>
+  </si>
+  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/bc/95/c5/75b609314a8dfe8b7ece83c446bc47ce.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/8f/3d/d4/265222415e48466431578e5d50528ab8.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ba/fa/f2/518ce45e3aaccf3523b32321b7710d9a.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/59/e7/74/68080c04130bb376a971ea54196b6f60.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/23/cc/4d/4e8dc54b550ca5438b8f3b4d5e786f7e.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/20/10/20/0590c71068184207b66d1a0e6cd6e0af.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/32/b6/d3/0ca66b5a987df2f056000054457bf3c2.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/84/6c/56/782eb3f6491384553aaf71d0ac4f7661.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/b4/2c/b9/59569bb010e754e338314671c16c84a8.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/39/14/47/cc020b37a155e60301076ca55fc23c57.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/43/b8/49/e2fc95922f52f6b546b3159e2e64454d.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/c0/be/c1/1856d5ff1185a7c14d038704c01a4269.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/25/ce/b9/421962b198f5250c9a87f5ff4d6b3bb0.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ea/6d/92/5917ee4c9a1124d82298b4695cd742b1.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/5c/39/8f/47a8209e6f2ec87da7a9d074610c834d.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/8c/80/88/c83c3f2fe6281a892666b5d3b3a0b963.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ce/82/d3/9bb25806d67aeb8ff3d583bcce9442e6.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/a9/5b/c9/d83c2f42fd59ea8fbb1c10a4b9ccc787.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/7e/30/c9/e1b87f07a82762db5c122516dc5dd51c.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/84/dd/92/991b033392f01d334d1ce248d69e1daa.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/05/49/8f/e093321a9f3ed55fe77e8c83bfca8c55.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/77/b0/69/63bbae55fe5a5a096392c6d325e8fc95.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/d4/7e/c9/72e19580d556fa02d030cc6e77d1c6fd.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/c7/a1/73/79e54ec11e29656703784d7ad6eeae22.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/a5/a0/34/8d34647a6f97612e08a6869a6a7729ab.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/41/c4/04/18c6cf90e258545542577f9a2a9185c3.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/61/f7/fb/63445f959fb5036ba2504f7e1b91eecf.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/a7/fe/de/bc4d3269a46128e7c9c9ecb3f0e4c213.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/2c/63/b3/c84e4dd1cb2a41394e8086f52a26bd15.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/43/2c/ac/16c0f54cb6034936f9dcd799344bcb5a.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/02/52/15/e45e133fe9a563b67cb15e0c2c3e81dc.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/9b/82/57/da1f2bb909396656918a1ebcef4891b9.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/8e/29/10/17ea04e162b7f63bf7bc178b7597bb21.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/90/1e/d6/483ad20a073f3e2165c8b95b9b00bbd0.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/94/c2/a9/d47791500dc8a1c938439bcce17dbcc1.jpg</t>
-  </si>
-  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/41/cd/bb/1602f9d78df7386eb039261a9a8ea17d.jpg</t>
   </si>
   <si>
@@ -910,16 +916,10 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/fb/78/0c/f88ea8836a305f29cfe7f21a0f4029f2.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/5b/84/32/f01e0aa28c9de9cc48e73dccc32eedc0.jpg</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/99/98/0c/82ec73f0993068fd307c7cc101e401a0.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/e3/1e/c1/0bee95c3d68e574a6b71979858500858.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/6c/b1/87/9da32235b3a0d50ad5e2b3c5bb6a4a13.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/01/be/79/15314677596e5076541f60fc98999dbe.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/a7/37/40/2153b8aad82a11b9d588de97fec3a724.jpg</t>
@@ -1457,7 +1457,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>277465334</v>
+        <v>277466537</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -1542,7 +1542,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>277007015</v>
+        <v>276944892</v>
       </c>
       <c r="B15" t="s">
         <v>18</v>
@@ -1559,7 +1559,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>276944892</v>
+        <v>276614493</v>
       </c>
       <c r="B16" t="s">
         <v>19</v>
@@ -1576,7 +1576,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>276614493</v>
+        <v>276539826</v>
       </c>
       <c r="B17" t="s">
         <v>20</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>276539826</v>
+        <v>276515327</v>
       </c>
       <c r="B18" t="s">
         <v>21</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>276515327</v>
+        <v>276314708</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
@@ -1644,7 +1644,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>276110349</v>
+        <v>276250848</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
@@ -1780,7 +1780,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>271967379</v>
+        <v>273872197</v>
       </c>
       <c r="B29" t="s">
         <v>32</v>
@@ -2154,7 +2154,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51">
-        <v>277409699</v>
+        <v>277311651</v>
       </c>
       <c r="B51" t="s">
         <v>54</v>
@@ -2171,7 +2171,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52">
-        <v>277311651</v>
+        <v>277311630</v>
       </c>
       <c r="B52" t="s">
         <v>55</v>
@@ -2188,7 +2188,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53">
-        <v>277311630</v>
+        <v>277164948</v>
       </c>
       <c r="B53" t="s">
         <v>56</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54">
-        <v>277164948</v>
+        <v>277068413</v>
       </c>
       <c r="B54" t="s">
         <v>57</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55">
-        <v>277068413</v>
+        <v>277065642</v>
       </c>
       <c r="B55" t="s">
         <v>58</v>
@@ -2239,7 +2239,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56">
-        <v>277065642</v>
+        <v>277041250</v>
       </c>
       <c r="B56" t="s">
         <v>59</v>
@@ -2256,7 +2256,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57">
-        <v>277041250</v>
+        <v>277014407</v>
       </c>
       <c r="B57" t="s">
         <v>60</v>
@@ -2273,7 +2273,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58">
-        <v>277039291</v>
+        <v>276639232</v>
       </c>
       <c r="B58" t="s">
         <v>61</v>
@@ -2290,7 +2290,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59">
-        <v>277014407</v>
+        <v>276489194</v>
       </c>
       <c r="B59" t="s">
         <v>62</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60">
-        <v>276639232</v>
+        <v>276465090</v>
       </c>
       <c r="B60" t="s">
         <v>63</v>
@@ -2358,7 +2358,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63">
-        <v>276314708</v>
+        <v>276281988</v>
       </c>
       <c r="B63" t="s">
         <v>66</v>
@@ -2375,7 +2375,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64">
-        <v>276305472</v>
+        <v>276110276</v>
       </c>
       <c r="B64" t="s">
         <v>67</v>
@@ -2392,7 +2392,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65">
-        <v>276281988</v>
+        <v>275386982</v>
       </c>
       <c r="B65" t="s">
         <v>68</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66">
-        <v>276110276</v>
+        <v>274638659</v>
       </c>
       <c r="B66" t="s">
         <v>69</v>
@@ -2426,7 +2426,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67">
-        <v>275338696</v>
+        <v>274544634</v>
       </c>
       <c r="B67" t="s">
         <v>70</v>
@@ -2443,7 +2443,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68">
-        <v>274544634</v>
+        <v>274516951</v>
       </c>
       <c r="B68" t="s">
         <v>71</v>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69">
-        <v>274516951</v>
+        <v>274405521</v>
       </c>
       <c r="B69" t="s">
         <v>72</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70">
-        <v>274405521</v>
+        <v>273990229</v>
       </c>
       <c r="B70" t="s">
         <v>73</v>
@@ -2494,7 +2494,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71">
-        <v>273990229</v>
+        <v>273227290</v>
       </c>
       <c r="B71" t="s">
         <v>74</v>
@@ -2800,7 +2800,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89">
-        <v>277437876</v>
+        <v>277484785</v>
       </c>
       <c r="B89" t="s">
         <v>91</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90">
-        <v>277356193</v>
+        <v>277437876</v>
       </c>
       <c r="B90" t="s">
         <v>92</v>
@@ -2834,7 +2834,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91">
-        <v>277356031</v>
+        <v>277356193</v>
       </c>
       <c r="B91" t="s">
         <v>93</v>
@@ -2851,7 +2851,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92">
-        <v>277175955</v>
+        <v>277356031</v>
       </c>
       <c r="B92" t="s">
         <v>94</v>
@@ -2868,7 +2868,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93">
-        <v>277030799</v>
+        <v>277175955</v>
       </c>
       <c r="B93" t="s">
         <v>95</v>
@@ -2885,7 +2885,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94">
-        <v>276944868</v>
+        <v>277039291</v>
       </c>
       <c r="B94" t="s">
         <v>96</v>
@@ -2902,7 +2902,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95">
-        <v>276925932</v>
+        <v>277030799</v>
       </c>
       <c r="B95" t="s">
         <v>97</v>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96">
-        <v>276802409</v>
+        <v>276944868</v>
       </c>
       <c r="B96" t="s">
         <v>98</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97">
-        <v>276500230</v>
+        <v>276925932</v>
       </c>
       <c r="B97" t="s">
         <v>99</v>
@@ -2953,7 +2953,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98">
-        <v>276489194</v>
+        <v>276802409</v>
       </c>
       <c r="B98" t="s">
         <v>100</v>
@@ -2970,7 +2970,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99">
-        <v>276465090</v>
+        <v>276500230</v>
       </c>
       <c r="B99" t="s">
         <v>101</v>
